--- a/PM12.xlsx
+++ b/PM12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\_COURSES\2026_2\pm-course-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0D0D93-75FB-4A64-8F2A-C9DCB2DF33C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B772CF3D-C613-46DC-892B-B1108C547E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="16395" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Программа" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="81">
   <si>
     <t>Неделя</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Долг на экзамен</t>
+  </si>
+  <si>
+    <t>Қатпанов Жарас Нұрлұбекұлы</t>
   </si>
 </sst>
 </file>
@@ -635,13 +638,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -967,15 +970,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="49.1328125" customWidth="1"/>
-    <col min="3" max="3" width="46.73046875" customWidth="1"/>
-    <col min="4" max="4" width="40.59765625" customWidth="1"/>
-    <col min="7" max="7" width="21.1328125" customWidth="1"/>
+    <col min="2" max="2" width="49.140625" customWidth="1"/>
+    <col min="3" max="3" width="46.7109375" customWidth="1"/>
+    <col min="4" max="4" width="40.5703125" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>33</v>
       </c>
@@ -992,7 +995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1002,7 +1005,7 @@
       <c r="E2" s="1"/>
       <c r="G2" s="16"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1012,7 +1015,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="30"/>
     </row>
-    <row r="4" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1021,7 +1024,7 @@
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1030,7 +1033,7 @@
       <c r="D5" s="3"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:7" ht="91.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="91.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1040,7 +1043,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1050,7 +1053,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="14"/>
     </row>
-    <row r="8" spans="1:7" ht="84.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="84.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1061,7 +1064,7 @@
       <c r="F8" s="14"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1071,7 +1074,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="14"/>
     </row>
-    <row r="10" spans="1:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1082,7 +1085,7 @@
       <c r="F10" s="14"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1092,7 +1095,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="14"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1103,7 +1106,7 @@
       <c r="F12" s="14"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1113,7 +1116,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="14"/>
     </row>
-    <row r="14" spans="1:7" ht="71.650000000000006" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" ht="71.650000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1122,7 +1125,7 @@
       <c r="D14" s="3"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1131,7 +1134,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1140,12 +1143,12 @@
       <c r="D16" s="39"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:10" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="36"/>
       <c r="B17" s="36"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C18" s="4"/>
       <c r="G18" s="8"/>
       <c r="H18" s="9" t="s">
@@ -1158,7 +1161,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G19" s="10" t="s">
         <v>39</v>
       </c>
@@ -1175,7 +1178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G20" s="10" t="s">
         <v>40</v>
       </c>
@@ -1192,7 +1195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G21" s="11" t="s">
         <v>30</v>
       </c>
@@ -1209,7 +1212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B22" s="29"/>
       <c r="G22" t="s">
         <v>41</v>
@@ -1219,7 +1222,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G23" t="s">
         <v>42</v>
       </c>
@@ -1235,7 +1238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>43</v>
       </c>
@@ -1243,7 +1246,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
         <v>44</v>
       </c>
@@ -1264,40 +1267,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BC38"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.1328125" customWidth="1"/>
-    <col min="2" max="2" width="39.3984375" customWidth="1"/>
-    <col min="18" max="18" width="9.59765625" customWidth="1"/>
-    <col min="19" max="20" width="8.59765625" customWidth="1"/>
-    <col min="21" max="21" width="8.86328125" customWidth="1"/>
-    <col min="22" max="22" width="9.265625" customWidth="1"/>
-    <col min="25" max="25" width="8.86328125" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" customWidth="1"/>
+    <col min="2" max="2" width="39.42578125" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" customWidth="1"/>
+    <col min="19" max="20" width="8.5703125" customWidth="1"/>
+    <col min="21" max="21" width="8.85546875" customWidth="1"/>
+    <col min="22" max="22" width="9.28515625" customWidth="1"/>
+    <col min="25" max="25" width="8.85546875" customWidth="1"/>
     <col min="48" max="48" width="10" customWidth="1"/>
-    <col min="55" max="55" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="C2" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
       <c r="W2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1355,7 +1358,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1420,7 +1423,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1485,7 +1488,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1550,7 +1553,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1615,7 +1618,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1680,7 +1683,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1745,7 +1748,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1810,7 +1813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1875,7 +1878,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1940,7 +1943,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2005,7 +2008,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2070,7 +2073,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:35" hidden="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2137,7 +2140,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:35" hidden="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2207,7 +2210,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:55" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:55" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2274,106 +2277,106 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:55" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:55" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="34">
         <v>1</v>
       </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33">
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34">
         <v>2</v>
       </c>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33">
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
         <v>3</v>
       </c>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33">
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
         <v>4</v>
       </c>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33">
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34">
         <v>5</v>
       </c>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33">
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34">
         <v>6</v>
       </c>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="33">
+      <c r="S21" s="34"/>
+      <c r="T21" s="34"/>
+      <c r="U21" s="34">
         <v>7</v>
       </c>
-      <c r="V21" s="33"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="33">
+      <c r="V21" s="34"/>
+      <c r="W21" s="34"/>
+      <c r="X21" s="34">
         <v>8</v>
       </c>
-      <c r="Y21" s="33"/>
-      <c r="Z21" s="33"/>
-      <c r="AA21" s="33">
+      <c r="Y21" s="34"/>
+      <c r="Z21" s="34"/>
+      <c r="AA21" s="34">
         <v>9</v>
       </c>
-      <c r="AB21" s="33"/>
-      <c r="AC21" s="33"/>
-      <c r="AD21" s="33">
+      <c r="AB21" s="34"/>
+      <c r="AC21" s="34"/>
+      <c r="AD21" s="34">
         <v>10</v>
       </c>
-      <c r="AE21" s="33"/>
-      <c r="AF21" s="33"/>
-      <c r="AG21" s="33">
+      <c r="AE21" s="34"/>
+      <c r="AF21" s="34"/>
+      <c r="AG21" s="34">
         <v>11</v>
       </c>
-      <c r="AH21" s="33"/>
-      <c r="AI21" s="33"/>
-      <c r="AJ21" s="33">
+      <c r="AH21" s="34"/>
+      <c r="AI21" s="34"/>
+      <c r="AJ21" s="34">
         <v>12</v>
       </c>
-      <c r="AK21" s="33"/>
-      <c r="AL21" s="33"/>
-      <c r="AM21" s="33">
+      <c r="AK21" s="34"/>
+      <c r="AL21" s="34"/>
+      <c r="AM21" s="34">
         <v>13</v>
       </c>
-      <c r="AN21" s="33"/>
-      <c r="AO21" s="33"/>
-      <c r="AP21" s="33">
+      <c r="AN21" s="34"/>
+      <c r="AO21" s="34"/>
+      <c r="AP21" s="34">
         <v>14</v>
       </c>
-      <c r="AQ21" s="33"/>
-      <c r="AR21" s="33"/>
-      <c r="AS21" s="33">
+      <c r="AQ21" s="34"/>
+      <c r="AR21" s="34"/>
+      <c r="AS21" s="34">
         <v>15</v>
       </c>
-      <c r="AT21" s="33"/>
-      <c r="AU21" s="33"/>
-      <c r="AV21" s="33" t="s">
+      <c r="AT21" s="34"/>
+      <c r="AU21" s="34"/>
+      <c r="AV21" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="AW21" s="33"/>
-      <c r="AX21" s="33"/>
-      <c r="AY21" s="33" t="s">
+      <c r="AW21" s="34"/>
+      <c r="AX21" s="34"/>
+      <c r="AY21" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="AZ21" s="33"/>
-      <c r="BA21" s="33"/>
-      <c r="BB21" s="33" t="s">
+      <c r="AZ21" s="34"/>
+      <c r="BA21" s="34"/>
+      <c r="BB21" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="BC21" s="33"/>
-    </row>
-    <row r="22" spans="1:55" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="BC21" s="34"/>
+    </row>
+    <row r="22" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>19</v>
       </c>
@@ -2410,9 +2413,9 @@
       <c r="AG22" s="6"/>
       <c r="AH22" s="6"/>
       <c r="AI22" s="6"/>
-      <c r="AJ22" s="35"/>
-      <c r="AK22" s="35"/>
-      <c r="AL22" s="35"/>
+      <c r="AJ22" s="33"/>
+      <c r="AK22" s="33"/>
+      <c r="AL22" s="33"/>
       <c r="AM22" s="6"/>
       <c r="AN22" s="6"/>
       <c r="AO22" s="6"/>
@@ -2423,7 +2426,7 @@
       <c r="AT22" s="6"/>
       <c r="AU22" s="6"/>
     </row>
-    <row r="23" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>5</v>
       </c>
@@ -2590,7 +2593,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>1</v>
       </c>
@@ -2766,7 +2769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>2</v>
       </c>
@@ -2942,7 +2945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>3</v>
       </c>
@@ -3118,7 +3121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>4</v>
       </c>
@@ -3294,7 +3297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>5</v>
       </c>
@@ -3470,7 +3473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>6</v>
       </c>
@@ -3646,7 +3649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>7</v>
       </c>
@@ -3822,7 +3825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>8</v>
       </c>
@@ -3998,7 +4001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>9</v>
       </c>
@@ -4174,7 +4177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>10</v>
       </c>
@@ -4350,7 +4353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>11</v>
       </c>
@@ -4526,7 +4529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:55" hidden="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:55" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>12</v>
       </c>
@@ -4702,7 +4705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:55" hidden="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:55" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>13</v>
       </c>
@@ -4878,7 +4881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:55" hidden="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:55" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>14</v>
       </c>
@@ -5054,7 +5057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:55" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
       <c r="B38" s="12" t="s">
         <v>17</v>
@@ -5243,6 +5246,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="R21:T21"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
     <mergeCell ref="AJ22:AL22"/>
     <mergeCell ref="AV21:AX21"/>
     <mergeCell ref="AY21:BA21"/>
@@ -5256,13 +5266,6 @@
     <mergeCell ref="AM21:AO21"/>
     <mergeCell ref="AP21:AR21"/>
     <mergeCell ref="AS21:AU21"/>
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="R21:T21"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C24:AU37">
@@ -5282,40 +5285,40 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BC38"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.1328125" customWidth="1"/>
-    <col min="2" max="2" width="39.3984375" customWidth="1"/>
-    <col min="18" max="18" width="7.86328125" customWidth="1"/>
-    <col min="19" max="20" width="8.59765625" customWidth="1"/>
-    <col min="21" max="21" width="8.86328125" customWidth="1"/>
-    <col min="22" max="22" width="9.265625" customWidth="1"/>
-    <col min="25" max="25" width="8.86328125" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" customWidth="1"/>
+    <col min="2" max="2" width="39.42578125" customWidth="1"/>
+    <col min="18" max="18" width="7.85546875" customWidth="1"/>
+    <col min="19" max="20" width="8.5703125" customWidth="1"/>
+    <col min="21" max="21" width="8.85546875" customWidth="1"/>
+    <col min="22" max="22" width="9.28515625" customWidth="1"/>
+    <col min="25" max="25" width="8.85546875" customWidth="1"/>
     <col min="48" max="48" width="10" customWidth="1"/>
-    <col min="55" max="55" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="C2" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
       <c r="W2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -5373,7 +5376,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -5438,7 +5441,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -5503,7 +5506,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -5568,7 +5571,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -5633,7 +5636,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -5698,7 +5701,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -5763,7 +5766,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -5828,7 +5831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -5893,7 +5896,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -5958,12 +5961,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
@@ -6023,12 +6026,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
@@ -6088,12 +6091,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
@@ -6153,12 +6156,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
@@ -6221,11 +6224,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:55" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>14</v>
       </c>
-      <c r="B17" s="1"/>
+      <c r="B17" t="s">
+        <v>76</v>
+      </c>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
       <c r="E17" s="25"/>
@@ -6288,106 +6293,106 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:55" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:55" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="34">
         <v>1</v>
       </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33">
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34">
         <v>2</v>
       </c>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33">
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34">
         <v>3</v>
       </c>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33">
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34">
         <v>4</v>
       </c>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33">
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34">
         <v>5</v>
       </c>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33">
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34">
         <v>6</v>
       </c>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="33">
+      <c r="S21" s="34"/>
+      <c r="T21" s="34"/>
+      <c r="U21" s="34">
         <v>7</v>
       </c>
-      <c r="V21" s="33"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="33">
+      <c r="V21" s="34"/>
+      <c r="W21" s="34"/>
+      <c r="X21" s="34">
         <v>8</v>
       </c>
-      <c r="Y21" s="33"/>
-      <c r="Z21" s="33"/>
-      <c r="AA21" s="33">
+      <c r="Y21" s="34"/>
+      <c r="Z21" s="34"/>
+      <c r="AA21" s="34">
         <v>9</v>
       </c>
-      <c r="AB21" s="33"/>
-      <c r="AC21" s="33"/>
-      <c r="AD21" s="33">
+      <c r="AB21" s="34"/>
+      <c r="AC21" s="34"/>
+      <c r="AD21" s="34">
         <v>10</v>
       </c>
-      <c r="AE21" s="33"/>
-      <c r="AF21" s="33"/>
-      <c r="AG21" s="33">
+      <c r="AE21" s="34"/>
+      <c r="AF21" s="34"/>
+      <c r="AG21" s="34">
         <v>11</v>
       </c>
-      <c r="AH21" s="33"/>
-      <c r="AI21" s="33"/>
-      <c r="AJ21" s="33">
+      <c r="AH21" s="34"/>
+      <c r="AI21" s="34"/>
+      <c r="AJ21" s="34">
         <v>12</v>
       </c>
-      <c r="AK21" s="33"/>
-      <c r="AL21" s="33"/>
-      <c r="AM21" s="33">
+      <c r="AK21" s="34"/>
+      <c r="AL21" s="34"/>
+      <c r="AM21" s="34">
         <v>13</v>
       </c>
-      <c r="AN21" s="33"/>
-      <c r="AO21" s="33"/>
-      <c r="AP21" s="33">
+      <c r="AN21" s="34"/>
+      <c r="AO21" s="34"/>
+      <c r="AP21" s="34">
         <v>14</v>
       </c>
-      <c r="AQ21" s="33"/>
-      <c r="AR21" s="33"/>
-      <c r="AS21" s="33">
+      <c r="AQ21" s="34"/>
+      <c r="AR21" s="34"/>
+      <c r="AS21" s="34">
         <v>15</v>
       </c>
-      <c r="AT21" s="33"/>
-      <c r="AU21" s="33"/>
-      <c r="AV21" s="33" t="s">
+      <c r="AT21" s="34"/>
+      <c r="AU21" s="34"/>
+      <c r="AV21" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="AW21" s="33"/>
-      <c r="AX21" s="33"/>
-      <c r="AY21" s="33" t="s">
+      <c r="AW21" s="34"/>
+      <c r="AX21" s="34"/>
+      <c r="AY21" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="AZ21" s="33"/>
-      <c r="BA21" s="33"/>
-      <c r="BB21" s="33" t="s">
+      <c r="AZ21" s="34"/>
+      <c r="BA21" s="34"/>
+      <c r="BB21" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="BC21" s="33"/>
-    </row>
-    <row r="22" spans="1:55" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="BC21" s="34"/>
+    </row>
+    <row r="22" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>19</v>
       </c>
@@ -6406,9 +6411,9 @@
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="35"/>
+      <c r="R22" s="33"/>
+      <c r="S22" s="33"/>
+      <c r="T22" s="33"/>
       <c r="U22" s="6"/>
       <c r="V22" s="6"/>
       <c r="W22" s="6"/>
@@ -6437,7 +6442,7 @@
       <c r="AT22" s="6"/>
       <c r="AU22" s="6"/>
     </row>
-    <row r="23" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>5</v>
       </c>
@@ -6604,7 +6609,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>1</v>
       </c>
@@ -6780,7 +6785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>2</v>
       </c>
@@ -6956,7 +6961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>3</v>
       </c>
@@ -7132,7 +7137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>4</v>
       </c>
@@ -7308,7 +7313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>5</v>
       </c>
@@ -7484,7 +7489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>6</v>
       </c>
@@ -7660,7 +7665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>7</v>
       </c>
@@ -7836,7 +7841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>8</v>
       </c>
@@ -8012,7 +8017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>9</v>
       </c>
@@ -8188,13 +8193,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>10</v>
       </c>
       <c r="B33" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>Мұратова Назылы Асхатқызы</v>
+        <v>Қатпанов Жарас Нұрлұбекұлы</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>47</v>
@@ -8364,13 +8369,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>11</v>
       </c>
       <c r="B34" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>Нургалиев Бақдәулет Ерланұлы</v>
+        <v>Мұратова Назылы Асхатқызы</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>47</v>
@@ -8540,13 +8545,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>12</v>
       </c>
       <c r="B35" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>Нұрислам Айдана Қазыбекқызы</v>
+        <v>Нургалиев Бақдәулет Ерланұлы</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>47</v>
@@ -8716,13 +8721,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:55" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>13</v>
       </c>
       <c r="B36" s="1" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">Рақымжанұлы Ералы </v>
+        <v>Нұрислам Айдана Қазыбекқызы</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>47</v>
@@ -8892,13 +8897,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:55" hidden="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>14</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v xml:space="preserve">Рақымжанұлы Ералы </v>
       </c>
       <c r="C37" s="13" t="s">
         <v>47</v>
@@ -9064,7 +9069,7 @@
         <v>4.4444444444444446</v>
       </c>
     </row>
-    <row r="38" spans="1:55" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
       <c r="B38" s="12" t="s">
         <v>17</v>
@@ -9253,6 +9258,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="R21:T21"/>
+    <mergeCell ref="U21:W21"/>
+    <mergeCell ref="X21:Z21"/>
+    <mergeCell ref="AA21:AC21"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:N21"/>
     <mergeCell ref="R22:T22"/>
     <mergeCell ref="BB21:BC21"/>
     <mergeCell ref="AJ21:AL21"/>
@@ -9263,16 +9278,6 @@
     <mergeCell ref="AY21:BA21"/>
     <mergeCell ref="AG21:AI21"/>
     <mergeCell ref="AD21:AF21"/>
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="R21:T21"/>
-    <mergeCell ref="U21:W21"/>
-    <mergeCell ref="X21:Z21"/>
-    <mergeCell ref="AA21:AC21"/>
   </mergeCells>
   <conditionalFormatting sqref="C24:AU37">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">

--- a/PM12.xlsx
+++ b/PM12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\_COURSES\2026_2\pm-course-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\repos\courses\journals-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B772CF3D-C613-46DC-892B-B1108C547E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52105AF-A198-45F0-8173-3301BF0F031A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Программа" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="81">
   <si>
     <t>Неделя</t>
   </si>
@@ -638,13 +638,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -661,8 +661,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -970,15 +970,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="49.140625" customWidth="1"/>
-    <col min="3" max="3" width="46.7109375" customWidth="1"/>
-    <col min="4" max="4" width="40.5703125" customWidth="1"/>
-    <col min="7" max="7" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="49.109375" customWidth="1"/>
+    <col min="3" max="3" width="46.6640625" customWidth="1"/>
+    <col min="4" max="4" width="40.5546875" customWidth="1"/>
+    <col min="7" max="7" width="21.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>33</v>
       </c>
@@ -995,7 +995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1005,7 +1005,7 @@
       <c r="E2" s="1"/>
       <c r="G2" s="16"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1015,7 +1015,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="30"/>
     </row>
-    <row r="4" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1024,7 +1024,7 @@
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1033,7 +1033,7 @@
       <c r="D5" s="3"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:7" ht="91.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1043,7 +1043,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1053,7 +1053,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="14"/>
     </row>
-    <row r="8" spans="1:7" ht="84.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="84.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1064,7 +1064,7 @@
       <c r="F8" s="14"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1074,7 +1074,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="14"/>
     </row>
-    <row r="10" spans="1:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1085,7 +1085,7 @@
       <c r="F10" s="14"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1095,7 +1095,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="14"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1106,7 +1106,7 @@
       <c r="F12" s="14"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1116,7 +1116,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="14"/>
     </row>
-    <row r="14" spans="1:7" ht="71.650000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="71.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1125,7 +1125,7 @@
       <c r="D14" s="3"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1134,7 +1134,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1143,12 +1143,12 @@
       <c r="D16" s="39"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="36"/>
       <c r="B17" s="36"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C18" s="4"/>
       <c r="G18" s="8"/>
       <c r="H18" s="9" t="s">
@@ -1161,7 +1161,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G19" s="10" t="s">
         <v>39</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G20" s="10" t="s">
         <v>40</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G21" s="11" t="s">
         <v>30</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B22" s="29"/>
       <c r="G22" t="s">
         <v>41</v>
@@ -1222,7 +1222,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G23" t="s">
         <v>42</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G25" t="s">
         <v>43</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G26" t="s">
         <v>44</v>
       </c>
@@ -1267,40 +1267,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BC38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.140625" customWidth="1"/>
-    <col min="2" max="2" width="39.42578125" customWidth="1"/>
-    <col min="18" max="18" width="9.5703125" customWidth="1"/>
-    <col min="19" max="20" width="8.5703125" customWidth="1"/>
-    <col min="21" max="21" width="8.85546875" customWidth="1"/>
-    <col min="22" max="22" width="9.28515625" customWidth="1"/>
-    <col min="25" max="25" width="8.85546875" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" customWidth="1"/>
+    <col min="2" max="2" width="39.44140625" customWidth="1"/>
+    <col min="18" max="18" width="9.5546875" customWidth="1"/>
+    <col min="19" max="20" width="8.5546875" customWidth="1"/>
+    <col min="21" max="21" width="8.88671875" customWidth="1"/>
+    <col min="22" max="22" width="9.33203125" customWidth="1"/>
+    <col min="25" max="25" width="8.88671875" customWidth="1"/>
     <col min="48" max="48" width="10" customWidth="1"/>
-    <col min="55" max="55" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="C2" s="35" t="s">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="C2" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
       <c r="W2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1375,7 +1375,7 @@
       <c r="J4" s="26"/>
       <c r="S4">
         <f t="shared" ref="S4:S17" si="0">U4+AE4-AA4</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T4" t="str">
         <f>_xlfn.CONCAT("/", Программа!$J$23)</f>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="U4">
         <f>SUM(C4:F4)+Программа!$H$26*COUNTIF(C24:Z24, "+")+R4</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V4" t="str">
         <f>_xlfn.CONCAT("/",Программа!$H$21)</f>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AA4">
         <f t="shared" ref="AA4:AA17" si="2">U4-W4</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB4" s="17" t="s">
         <v>46</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AE4">
         <f>SUM(G4:J4)+COUNTIF(AA24:AU24, "+")*Программа!$H$26+AA4</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AF4" t="str">
         <f>_xlfn.CONCAT("/",Программа!$I$23)</f>
@@ -1417,13 +1417,13 @@
       </c>
       <c r="AG4" s="28">
         <f t="shared" ref="AG4:AG17" si="3">IF(AE4&gt;60, 100, ROUND(AE4/60*100, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1440,7 +1440,7 @@
       <c r="J5" s="26"/>
       <c r="S5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T5" t="str">
         <f t="shared" ref="T5:T17" si="4">T4</f>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="U5">
         <f>SUM(C5:F5)+Программа!$H$26*COUNTIF(C25:Z25, "+")+R5</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V5" t="str">
         <f t="shared" ref="V5:V17" si="5">V4</f>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AA5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB5" s="17" t="s">
         <v>46</v>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AE5">
         <f>SUM(G5:J5)+COUNTIF(AA25:AU25, "+")*Программа!$H$26+AA5</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AF5" t="str">
         <f t="shared" ref="AF5:AF17" si="7">$AF$4</f>
@@ -1482,13 +1482,13 @@
       </c>
       <c r="AG5" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1570,7 +1570,7 @@
       <c r="J7" s="27"/>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T7" t="str">
         <f t="shared" si="4"/>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="U7">
         <f>SUM(C7:F7)+Программа!$H$26*COUNTIF(C27:Z27, "+")+R7</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V7" t="str">
         <f t="shared" si="5"/>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AA7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB7" s="17" t="s">
         <v>46</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AE7">
         <f>SUM(G7:J7)+COUNTIF(AA27:AU27, "+")*Программа!$H$26+AA7</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AF7" t="str">
         <f t="shared" si="7"/>
@@ -1612,13 +1612,13 @@
       </c>
       <c r="AG7" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1635,7 +1635,7 @@
       <c r="J8" s="27"/>
       <c r="S8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T8" t="str">
         <f t="shared" si="4"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="U8">
         <f>SUM(C8:F8)+Программа!$H$26*COUNTIF(C28:Z28, "+")+R8</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V8" t="str">
         <f t="shared" si="5"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AA8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB8" s="17" t="s">
         <v>46</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AE8">
         <f>SUM(G8:J8)+COUNTIF(AA28:AU28, "+")*Программа!$H$26+AA8</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AF8" t="str">
         <f t="shared" si="7"/>
@@ -1677,13 +1677,13 @@
       </c>
       <c r="AG8" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1700,7 +1700,7 @@
       <c r="J9" s="26"/>
       <c r="S9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T9" t="str">
         <f t="shared" si="4"/>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="U9">
         <f>SUM(C9:F9)+Программа!$H$26*COUNTIF(C29:Z29, "+")+R9</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V9" t="str">
         <f t="shared" si="5"/>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AA9">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB9" s="17" t="s">
         <v>46</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="AE9">
         <f>SUM(G9:J9)+COUNTIF(AA29:AU29, "+")*Программа!$H$26+AA9</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AF9" t="str">
         <f t="shared" si="7"/>
@@ -1742,13 +1742,13 @@
       </c>
       <c r="AG9" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1830,7 +1830,7 @@
       <c r="J11" s="27"/>
       <c r="S11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T11" t="str">
         <f t="shared" si="4"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="U11">
         <f>SUM(C11:F11)+Программа!$H$26*COUNTIF(C31:Z31, "+")+R11</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V11" t="str">
         <f t="shared" si="5"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AA11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB11" s="17" t="s">
         <v>46</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="AE11">
         <f>SUM(G11:J11)+COUNTIF(AA31:AU31, "+")*Программа!$H$26+AA11</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AF11" t="str">
         <f t="shared" si="7"/>
@@ -1872,13 +1872,13 @@
       </c>
       <c r="AG11" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1960,7 +1960,7 @@
       <c r="J13" s="26"/>
       <c r="S13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T13" t="str">
         <f t="shared" si="4"/>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="U13">
         <f>SUM(C13:F13)+Программа!$H$26*COUNTIF(C33:Z33, "+")+R13</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V13" t="str">
         <f t="shared" si="5"/>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="AA13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB13" s="17" t="s">
         <v>46</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AE13">
         <f>SUM(G13:J13)+COUNTIF(AA33:AU33, "+")*Программа!$H$26+AA13</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AF13" t="str">
         <f t="shared" si="7"/>
@@ -2002,13 +2002,13 @@
       </c>
       <c r="AG13" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2025,7 +2025,7 @@
       <c r="J14" s="26"/>
       <c r="S14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T14" t="str">
         <f t="shared" si="4"/>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="U14">
         <f>SUM(C14:F14)+Программа!$H$26*COUNTIF(C34:Z34, "+")+R14</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V14" t="str">
         <f t="shared" si="5"/>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AA14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB14" s="17" t="s">
         <v>46</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="AE14">
         <f>SUM(G14:J14)+COUNTIF(AA34:AU34, "+")*Программа!$H$26+AA14</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AF14" t="str">
         <f t="shared" si="7"/>
@@ -2067,13 +2067,13 @@
       </c>
       <c r="AG14" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:55" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:55" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2277,106 +2277,106 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:55" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:55" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="33">
         <v>1</v>
       </c>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34">
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33">
         <v>2</v>
       </c>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34">
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33">
         <v>3</v>
       </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34">
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33">
         <v>4</v>
       </c>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34">
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="33">
         <v>5</v>
       </c>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="34">
+      <c r="P21" s="33"/>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="33">
         <v>6</v>
       </c>
-      <c r="S21" s="34"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="34">
+      <c r="S21" s="33"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="33">
         <v>7</v>
       </c>
-      <c r="V21" s="34"/>
-      <c r="W21" s="34"/>
-      <c r="X21" s="34">
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="33">
         <v>8</v>
       </c>
-      <c r="Y21" s="34"/>
-      <c r="Z21" s="34"/>
-      <c r="AA21" s="34">
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="33"/>
+      <c r="AA21" s="33">
         <v>9</v>
       </c>
-      <c r="AB21" s="34"/>
-      <c r="AC21" s="34"/>
-      <c r="AD21" s="34">
+      <c r="AB21" s="33"/>
+      <c r="AC21" s="33"/>
+      <c r="AD21" s="33">
         <v>10</v>
       </c>
-      <c r="AE21" s="34"/>
-      <c r="AF21" s="34"/>
-      <c r="AG21" s="34">
+      <c r="AE21" s="33"/>
+      <c r="AF21" s="33"/>
+      <c r="AG21" s="33">
         <v>11</v>
       </c>
-      <c r="AH21" s="34"/>
-      <c r="AI21" s="34"/>
-      <c r="AJ21" s="34">
+      <c r="AH21" s="33"/>
+      <c r="AI21" s="33"/>
+      <c r="AJ21" s="33">
         <v>12</v>
       </c>
-      <c r="AK21" s="34"/>
-      <c r="AL21" s="34"/>
-      <c r="AM21" s="34">
+      <c r="AK21" s="33"/>
+      <c r="AL21" s="33"/>
+      <c r="AM21" s="33">
         <v>13</v>
       </c>
-      <c r="AN21" s="34"/>
-      <c r="AO21" s="34"/>
-      <c r="AP21" s="34">
+      <c r="AN21" s="33"/>
+      <c r="AO21" s="33"/>
+      <c r="AP21" s="33">
         <v>14</v>
       </c>
-      <c r="AQ21" s="34"/>
-      <c r="AR21" s="34"/>
-      <c r="AS21" s="34">
+      <c r="AQ21" s="33"/>
+      <c r="AR21" s="33"/>
+      <c r="AS21" s="33">
         <v>15</v>
       </c>
-      <c r="AT21" s="34"/>
-      <c r="AU21" s="34"/>
-      <c r="AV21" s="34" t="s">
+      <c r="AT21" s="33"/>
+      <c r="AU21" s="33"/>
+      <c r="AV21" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="AW21" s="34"/>
-      <c r="AX21" s="34"/>
-      <c r="AY21" s="34" t="s">
+      <c r="AW21" s="33"/>
+      <c r="AX21" s="33"/>
+      <c r="AY21" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="AZ21" s="34"/>
-      <c r="BA21" s="34"/>
-      <c r="BB21" s="34" t="s">
+      <c r="AZ21" s="33"/>
+      <c r="BA21" s="33"/>
+      <c r="BB21" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="BC21" s="34"/>
-    </row>
-    <row r="22" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BC21" s="33"/>
+    </row>
+    <row r="22" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>19</v>
       </c>
@@ -2413,9 +2413,9 @@
       <c r="AG22" s="6"/>
       <c r="AH22" s="6"/>
       <c r="AI22" s="6"/>
-      <c r="AJ22" s="33"/>
-      <c r="AK22" s="33"/>
-      <c r="AL22" s="33"/>
+      <c r="AJ22" s="35"/>
+      <c r="AK22" s="35"/>
+      <c r="AL22" s="35"/>
       <c r="AM22" s="6"/>
       <c r="AN22" s="6"/>
       <c r="AO22" s="6"/>
@@ -2426,7 +2426,7 @@
       <c r="AT22" s="6"/>
       <c r="AU22" s="6"/>
     </row>
-    <row r="23" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>5</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>1</v>
       </c>
@@ -2602,13 +2602,13 @@
         <v>Ахмадиев Даулет Аубакерович</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F24" s="13" t="s">
         <v>47</v>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>2</v>
       </c>
@@ -2778,13 +2778,13 @@
         <v xml:space="preserve">Булатбекулы Ринат </v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F25" s="13" t="s">
         <v>47</v>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>3</v>
       </c>
@@ -2953,15 +2953,9 @@
         <f t="shared" si="9"/>
         <v>Гусева Алёна Сергеевна</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
       <c r="F26" s="13" t="s">
         <v>47</v>
       </c>
@@ -3090,15 +3084,15 @@
       </c>
       <c r="AV26" s="1">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW26" s="1">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX26" s="1">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY26" s="1">
         <f t="shared" si="13"/>
@@ -3114,14 +3108,14 @@
       </c>
       <c r="BB26" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC26" s="22">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:55" x14ac:dyDescent="0.25">
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="27" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>4</v>
       </c>
@@ -3130,13 +3124,13 @@
         <v>Жанузаков Аскар Манарбекулы</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>47</v>
@@ -3297,7 +3291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>5</v>
       </c>
@@ -3306,13 +3300,13 @@
         <v>Зарипханов Қуаныш Ерланұлы</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F28" s="13" t="s">
         <v>47</v>
@@ -3473,7 +3467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>6</v>
       </c>
@@ -3482,13 +3476,13 @@
         <v>Колесников Евгений Максимович</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>47</v>
@@ -3649,7 +3643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>7</v>
       </c>
@@ -3657,15 +3651,9 @@
         <f t="shared" si="9"/>
         <v>Крикуненко Данил Александрович</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
       <c r="F30" s="13" t="s">
         <v>47</v>
       </c>
@@ -3794,15 +3782,15 @@
       </c>
       <c r="AV30" s="1">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW30" s="1">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX30" s="1">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY30" s="1">
         <f t="shared" si="13"/>
@@ -3818,14 +3806,14 @@
       </c>
       <c r="BB30" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC30" s="22">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:55" x14ac:dyDescent="0.25">
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="31" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>8</v>
       </c>
@@ -3834,13 +3822,13 @@
         <v>Мягкова Софья Александровна</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>47</v>
@@ -4001,7 +3989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>9</v>
       </c>
@@ -4009,15 +3997,9 @@
         <f t="shared" si="9"/>
         <v>Смагулова Алина Айбековна</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
       <c r="F32" s="13" t="s">
         <v>47</v>
       </c>
@@ -4146,15 +4128,15 @@
       </c>
       <c r="AV32" s="1">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW32" s="1">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX32" s="1">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY32" s="1">
         <f t="shared" si="13"/>
@@ -4170,14 +4152,14 @@
       </c>
       <c r="BB32" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC32" s="22">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:55" x14ac:dyDescent="0.25">
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="33" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>10</v>
       </c>
@@ -4186,13 +4168,13 @@
         <v>Чеботарь Денис Константинович</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>47</v>
@@ -4353,7 +4335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>11</v>
       </c>
@@ -4362,13 +4344,13 @@
         <v>Шарыпов Александр Николаевич</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F34" s="13" t="s">
         <v>47</v>
@@ -4529,7 +4511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:55" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:55" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>12</v>
       </c>
@@ -4705,7 +4687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:55" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:55" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>13</v>
       </c>
@@ -4881,7 +4863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:55" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:55" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>14</v>
       </c>
@@ -5057,22 +5039,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11"/>
       <c r="B38" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C38" s="12">
         <f>COUNTIF(C24:C37, "+")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D38" s="12">
         <f t="shared" ref="D38:AU38" si="34">COUNTIF(D24:D37, "+")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E38" s="12">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="34"/>
@@ -5246,13 +5228,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="R21:T21"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
     <mergeCell ref="AJ22:AL22"/>
     <mergeCell ref="AV21:AX21"/>
     <mergeCell ref="AY21:BA21"/>
@@ -5266,6 +5241,13 @@
     <mergeCell ref="AM21:AO21"/>
     <mergeCell ref="AP21:AR21"/>
     <mergeCell ref="AS21:AU21"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="R21:T21"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C24:AU37">
@@ -5285,40 +5267,40 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BC38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.140625" customWidth="1"/>
-    <col min="2" max="2" width="39.42578125" customWidth="1"/>
-    <col min="18" max="18" width="7.85546875" customWidth="1"/>
-    <col min="19" max="20" width="8.5703125" customWidth="1"/>
-    <col min="21" max="21" width="8.85546875" customWidth="1"/>
-    <col min="22" max="22" width="9.28515625" customWidth="1"/>
-    <col min="25" max="25" width="8.85546875" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" customWidth="1"/>
+    <col min="2" max="2" width="39.44140625" customWidth="1"/>
+    <col min="18" max="18" width="7.88671875" customWidth="1"/>
+    <col min="19" max="20" width="8.5546875" customWidth="1"/>
+    <col min="21" max="21" width="8.88671875" customWidth="1"/>
+    <col min="22" max="22" width="9.33203125" customWidth="1"/>
+    <col min="25" max="25" width="8.88671875" customWidth="1"/>
     <col min="48" max="48" width="10" customWidth="1"/>
-    <col min="55" max="55" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="C2" s="35" t="s">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="C2" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
       <c r="W2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -5376,7 +5358,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -5393,7 +5375,7 @@
       <c r="J4" s="27"/>
       <c r="S4">
         <f>U4+AE4-AA4</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T4" t="str">
         <f>_xlfn.CONCAT("/", Программа!$J$23)</f>
@@ -5401,7 +5383,7 @@
       </c>
       <c r="U4">
         <f>SUM(C4:F4)+Программа!$H$26*COUNTIF(C24:Z24, "+")+R4</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V4" t="str">
         <f>_xlfn.CONCAT("/",Программа!$H$21)</f>
@@ -5416,7 +5398,7 @@
       </c>
       <c r="AA4">
         <f>U4-W4</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB4" s="17" t="s">
         <v>46</v>
@@ -5427,7 +5409,7 @@
       </c>
       <c r="AE4">
         <f>SUM(G4:J4)+COUNTIF(AA24:AU24, "+")*Программа!$H$26+AA4</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AF4" t="str">
         <f>_xlfn.CONCAT("/",Программа!$I$23)</f>
@@ -5435,13 +5417,13 @@
       </c>
       <c r="AG4" s="28">
         <f>IF(AE4&gt;60, 100, ROUND(AE4/60*100, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -5458,7 +5440,7 @@
       <c r="J5" s="27"/>
       <c r="S5">
         <f t="shared" ref="S5:S17" si="0">U5+AE5-AA5</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T5" t="str">
         <f>T4</f>
@@ -5466,7 +5448,7 @@
       </c>
       <c r="U5">
         <f>SUM(C5:F5)+Программа!$H$26*COUNTIF(C25:Z25, "+")+R5</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V5" t="str">
         <f>V4</f>
@@ -5481,7 +5463,7 @@
       </c>
       <c r="AA5">
         <f t="shared" ref="AA5:AA17" si="2">U5-W5</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB5" s="17" t="s">
         <v>46</v>
@@ -5492,7 +5474,7 @@
       </c>
       <c r="AE5">
         <f>SUM(G5:J5)+COUNTIF(AA25:AU25, "+")*Программа!$H$26+AA5</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AF5" t="str">
         <f t="shared" ref="AF5:AF17" si="3">$AF$4</f>
@@ -5500,13 +5482,13 @@
       </c>
       <c r="AG5" s="28">
         <f t="shared" ref="AG5:AG17" si="4">IF(AE5&gt;60, 100, ROUND(AE5/60*100, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -5571,7 +5553,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -5588,7 +5570,7 @@
       <c r="J7" s="27"/>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T7" t="str">
         <f t="shared" si="5"/>
@@ -5596,7 +5578,7 @@
       </c>
       <c r="U7">
         <f>SUM(C7:F7)+Программа!$H$26*COUNTIF(C27:Z27, "+")+R7</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V7" t="str">
         <f t="shared" si="6"/>
@@ -5611,7 +5593,7 @@
       </c>
       <c r="AA7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB7" s="17" t="s">
         <v>46</v>
@@ -5622,7 +5604,7 @@
       </c>
       <c r="AE7">
         <f>SUM(G7:J7)+COUNTIF(AA27:AU27, "+")*Программа!$H$26+AA7</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AF7" t="str">
         <f t="shared" si="3"/>
@@ -5630,13 +5612,13 @@
       </c>
       <c r="AG7" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -5701,7 +5683,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -5766,7 +5748,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -5831,7 +5813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -5896,7 +5878,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -5961,7 +5943,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -6026,7 +6008,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -6043,7 +6025,7 @@
       <c r="J14" s="27"/>
       <c r="S14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T14" t="str">
         <f t="shared" si="5"/>
@@ -6051,7 +6033,7 @@
       </c>
       <c r="U14">
         <f>SUM(C14:F14)+Программа!$H$26*COUNTIF(C34:Z34, "+")+R14</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V14" t="str">
         <f t="shared" si="6"/>
@@ -6066,7 +6048,7 @@
       </c>
       <c r="AA14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB14" s="17" t="s">
         <v>46</v>
@@ -6077,7 +6059,7 @@
       </c>
       <c r="AE14">
         <f>SUM(G14:J14)+COUNTIF(AA34:AU34, "+")*Программа!$H$26+AA14</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AF14" t="str">
         <f t="shared" si="3"/>
@@ -6085,13 +6067,13 @@
       </c>
       <c r="AG14" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -6108,7 +6090,7 @@
       <c r="J15" s="27"/>
       <c r="S15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T15" t="str">
         <f t="shared" si="5"/>
@@ -6116,7 +6098,7 @@
       </c>
       <c r="U15">
         <f>SUM(C15:F15)+Программа!$H$26*COUNTIF(C35:Z35, "+")+R15</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V15" t="str">
         <f t="shared" si="6"/>
@@ -6131,7 +6113,7 @@
       </c>
       <c r="AA15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB15" s="17" t="s">
         <v>46</v>
@@ -6142,7 +6124,7 @@
       </c>
       <c r="AE15">
         <f>SUM(G15:J15)+COUNTIF(AA35:AU35, "+")*Программа!$H$26+AA15</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AF15" t="str">
         <f t="shared" si="3"/>
@@ -6150,13 +6132,13 @@
       </c>
       <c r="AG15" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -6176,7 +6158,7 @@
       </c>
       <c r="S16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T16" t="str">
         <f t="shared" si="5"/>
@@ -6184,7 +6166,7 @@
       </c>
       <c r="U16">
         <f>SUM(C16:F16)+Программа!$H$26*COUNTIF(C36:Z36, "+")+R16</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V16" t="str">
         <f t="shared" si="6"/>
@@ -6199,7 +6181,7 @@
       </c>
       <c r="AA16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AB16" s="17" t="s">
         <v>46</v>
@@ -6210,7 +6192,7 @@
       </c>
       <c r="AE16">
         <f>SUM(G16:J16)+COUNTIF(AA36:AU36, "+")*Программа!$H$26+AA16</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AF16" t="str">
         <f t="shared" si="3"/>
@@ -6218,13 +6200,13 @@
       </c>
       <c r="AG16" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -6241,7 +6223,7 @@
       <c r="J17" s="27"/>
       <c r="S17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T17" t="str">
         <f t="shared" si="5"/>
@@ -6249,7 +6231,7 @@
       </c>
       <c r="U17">
         <f>SUM(C17:F17)+Программа!$H$26*COUNTIF(C37:Z37, "+")+R17</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="V17" t="str">
         <f t="shared" si="6"/>
@@ -6257,11 +6239,11 @@
       </c>
       <c r="W17">
         <f t="shared" ref="W17" si="8">U17</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="Y17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="s">
         <v>24</v>
@@ -6293,106 +6275,106 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:55" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:55" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="33">
         <v>1</v>
       </c>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34">
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33">
         <v>2</v>
       </c>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34">
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33">
         <v>3</v>
       </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34">
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33">
         <v>4</v>
       </c>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34">
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="33">
         <v>5</v>
       </c>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="34">
+      <c r="P21" s="33"/>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="33">
         <v>6</v>
       </c>
-      <c r="S21" s="34"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="34">
+      <c r="S21" s="33"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="33">
         <v>7</v>
       </c>
-      <c r="V21" s="34"/>
-      <c r="W21" s="34"/>
-      <c r="X21" s="34">
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="33">
         <v>8</v>
       </c>
-      <c r="Y21" s="34"/>
-      <c r="Z21" s="34"/>
-      <c r="AA21" s="34">
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="33"/>
+      <c r="AA21" s="33">
         <v>9</v>
       </c>
-      <c r="AB21" s="34"/>
-      <c r="AC21" s="34"/>
-      <c r="AD21" s="34">
+      <c r="AB21" s="33"/>
+      <c r="AC21" s="33"/>
+      <c r="AD21" s="33">
         <v>10</v>
       </c>
-      <c r="AE21" s="34"/>
-      <c r="AF21" s="34"/>
-      <c r="AG21" s="34">
+      <c r="AE21" s="33"/>
+      <c r="AF21" s="33"/>
+      <c r="AG21" s="33">
         <v>11</v>
       </c>
-      <c r="AH21" s="34"/>
-      <c r="AI21" s="34"/>
-      <c r="AJ21" s="34">
+      <c r="AH21" s="33"/>
+      <c r="AI21" s="33"/>
+      <c r="AJ21" s="33">
         <v>12</v>
       </c>
-      <c r="AK21" s="34"/>
-      <c r="AL21" s="34"/>
-      <c r="AM21" s="34">
+      <c r="AK21" s="33"/>
+      <c r="AL21" s="33"/>
+      <c r="AM21" s="33">
         <v>13</v>
       </c>
-      <c r="AN21" s="34"/>
-      <c r="AO21" s="34"/>
-      <c r="AP21" s="34">
+      <c r="AN21" s="33"/>
+      <c r="AO21" s="33"/>
+      <c r="AP21" s="33">
         <v>14</v>
       </c>
-      <c r="AQ21" s="34"/>
-      <c r="AR21" s="34"/>
-      <c r="AS21" s="34">
+      <c r="AQ21" s="33"/>
+      <c r="AR21" s="33"/>
+      <c r="AS21" s="33">
         <v>15</v>
       </c>
-      <c r="AT21" s="34"/>
-      <c r="AU21" s="34"/>
-      <c r="AV21" s="34" t="s">
+      <c r="AT21" s="33"/>
+      <c r="AU21" s="33"/>
+      <c r="AV21" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="AW21" s="34"/>
-      <c r="AX21" s="34"/>
-      <c r="AY21" s="34" t="s">
+      <c r="AW21" s="33"/>
+      <c r="AX21" s="33"/>
+      <c r="AY21" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="AZ21" s="34"/>
-      <c r="BA21" s="34"/>
-      <c r="BB21" s="34" t="s">
+      <c r="AZ21" s="33"/>
+      <c r="BA21" s="33"/>
+      <c r="BB21" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="BC21" s="34"/>
-    </row>
-    <row r="22" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BC21" s="33"/>
+    </row>
+    <row r="22" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>19</v>
       </c>
@@ -6411,9 +6393,9 @@
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="33"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="35"/>
       <c r="U22" s="6"/>
       <c r="V22" s="6"/>
       <c r="W22" s="6"/>
@@ -6442,7 +6424,7 @@
       <c r="AT22" s="6"/>
       <c r="AU22" s="6"/>
     </row>
-    <row r="23" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>5</v>
       </c>
@@ -6609,7 +6591,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>1</v>
       </c>
@@ -6618,13 +6600,13 @@
         <v>Абилов Шамиль Мерхатович</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F24" s="13" t="s">
         <v>47</v>
@@ -6785,7 +6767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>2</v>
       </c>
@@ -6794,13 +6776,13 @@
         <v>Амирханов Алмас Досымулы</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F25" s="13" t="s">
         <v>47</v>
@@ -6961,7 +6943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>3</v>
       </c>
@@ -6969,15 +6951,9 @@
         <f t="shared" si="9"/>
         <v>Ахметов Ариман Айдынович</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
       <c r="F26" s="13" t="s">
         <v>47</v>
       </c>
@@ -7106,15 +7082,15 @@
       </c>
       <c r="AV26" s="1">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW26" s="1">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX26" s="1">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY26" s="1">
         <f t="shared" si="13"/>
@@ -7130,14 +7106,14 @@
       </c>
       <c r="BB26" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC26" s="22">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:55" x14ac:dyDescent="0.25">
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="27" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>4</v>
       </c>
@@ -7146,13 +7122,13 @@
         <v>Байноллаев Шәріпхан Алмасұлы</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>47</v>
@@ -7313,7 +7289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>5</v>
       </c>
@@ -7321,15 +7297,9 @@
         <f t="shared" si="9"/>
         <v>Бақыт Әли Бақытұлы</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
       <c r="F28" s="13" t="s">
         <v>47</v>
       </c>
@@ -7458,15 +7428,15 @@
       </c>
       <c r="AV28" s="1">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW28" s="1">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX28" s="1">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY28" s="1">
         <f t="shared" si="13"/>
@@ -7482,14 +7452,14 @@
       </c>
       <c r="BB28" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC28" s="22">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:55" x14ac:dyDescent="0.25">
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="29" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>6</v>
       </c>
@@ -7497,15 +7467,9 @@
         <f t="shared" si="9"/>
         <v>Болатбеков Мирас Мерейұлы</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
       <c r="F29" s="13" t="s">
         <v>47</v>
       </c>
@@ -7634,15 +7598,15 @@
       </c>
       <c r="AV29" s="1">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW29" s="1">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX29" s="1">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY29" s="1">
         <f t="shared" si="13"/>
@@ -7658,14 +7622,14 @@
       </c>
       <c r="BB29" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC29" s="22">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:55" x14ac:dyDescent="0.25">
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="30" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>7</v>
       </c>
@@ -7673,15 +7637,9 @@
         <f t="shared" si="9"/>
         <v>Білісбек Жеңісбек Өмірбекұлы</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
       <c r="F30" s="13" t="s">
         <v>47</v>
       </c>
@@ -7810,15 +7768,15 @@
       </c>
       <c r="AV30" s="1">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW30" s="1">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX30" s="1">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY30" s="1">
         <f t="shared" si="13"/>
@@ -7834,14 +7792,14 @@
       </c>
       <c r="BB30" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC30" s="22">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:55" x14ac:dyDescent="0.25">
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="31" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>8</v>
       </c>
@@ -7849,15 +7807,9 @@
         <f t="shared" si="9"/>
         <v>Жорабек Даниел Талғатұлы</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
       <c r="F31" s="13" t="s">
         <v>47</v>
       </c>
@@ -7986,15 +7938,15 @@
       </c>
       <c r="AV31" s="1">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW31" s="1">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX31" s="1">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY31" s="1">
         <f t="shared" si="13"/>
@@ -8010,14 +7962,14 @@
       </c>
       <c r="BB31" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC31" s="22">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:55" x14ac:dyDescent="0.25">
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="32" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>9</v>
       </c>
@@ -8025,15 +7977,9 @@
         <f t="shared" si="9"/>
         <v>Кенжеәлі Нұрсат Сансызбайұлы</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
       <c r="F32" s="13" t="s">
         <v>47</v>
       </c>
@@ -8162,15 +8108,15 @@
       </c>
       <c r="AV32" s="1">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW32" s="1">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX32" s="1">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY32" s="1">
         <f t="shared" si="13"/>
@@ -8186,14 +8132,14 @@
       </c>
       <c r="BB32" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC32" s="22">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:55" x14ac:dyDescent="0.25">
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="33" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>10</v>
       </c>
@@ -8201,15 +8147,9 @@
         <f t="shared" si="9"/>
         <v>Қатпанов Жарас Нұрлұбекұлы</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>47</v>
-      </c>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
       <c r="F33" s="13" t="s">
         <v>47</v>
       </c>
@@ -8338,15 +8278,15 @@
       </c>
       <c r="AV33" s="1">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW33" s="1">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX33" s="1">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY33" s="1">
         <f t="shared" si="13"/>
@@ -8362,14 +8302,14 @@
       </c>
       <c r="BB33" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC33" s="22">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:55" x14ac:dyDescent="0.25">
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="34" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>11</v>
       </c>
@@ -8378,13 +8318,13 @@
         <v>Мұратова Назылы Асхатқызы</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F34" s="13" t="s">
         <v>47</v>
@@ -8545,7 +8485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>12</v>
       </c>
@@ -8554,13 +8494,13 @@
         <v>Нургалиев Бақдәулет Ерланұлы</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F35" s="13" t="s">
         <v>47</v>
@@ -8721,7 +8661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>13</v>
       </c>
@@ -8730,13 +8670,13 @@
         <v>Нұрислам Айдана Қазыбекқызы</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F36" s="13" t="s">
         <v>47</v>
@@ -8897,7 +8837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>14</v>
       </c>
@@ -8906,13 +8846,13 @@
         <v xml:space="preserve">Рақымжанұлы Ералы </v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F37" s="13" t="s">
         <v>47</v>
@@ -9069,22 +9009,22 @@
         <v>4.4444444444444446</v>
       </c>
     </row>
-    <row r="38" spans="1:55" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11"/>
       <c r="B38" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C38" s="12">
         <f>COUNTIF(C24:C37, "+")</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D38" s="12">
         <f t="shared" ref="D38:AU38" si="18">COUNTIF(D24:D37, "+")</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E38" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F38" s="12">
         <f t="shared" si="18"/>
@@ -9258,16 +9198,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="R21:T21"/>
-    <mergeCell ref="U21:W21"/>
-    <mergeCell ref="X21:Z21"/>
-    <mergeCell ref="AA21:AC21"/>
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:N21"/>
     <mergeCell ref="R22:T22"/>
     <mergeCell ref="BB21:BC21"/>
     <mergeCell ref="AJ21:AL21"/>
@@ -9278,6 +9208,16 @@
     <mergeCell ref="AY21:BA21"/>
     <mergeCell ref="AG21:AI21"/>
     <mergeCell ref="AD21:AF21"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="R21:T21"/>
+    <mergeCell ref="U21:W21"/>
+    <mergeCell ref="X21:Z21"/>
+    <mergeCell ref="AA21:AC21"/>
   </mergeCells>
   <conditionalFormatting sqref="C24:AU37">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">

--- a/PM12.xlsx
+++ b/PM12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\repos\courses\journals-store\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\_COURSES\2026_2\pm-course-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52105AF-A198-45F0-8173-3301BF0F031A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD5236E-196C-4F3C-A41D-BF1BB5A8A216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="16395" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Программа" sheetId="6" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -638,15 +641,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -659,10 +653,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -970,15 +973,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="49.109375" customWidth="1"/>
+    <col min="2" max="2" width="49.1328125" customWidth="1"/>
     <col min="3" max="3" width="46.6640625" customWidth="1"/>
-    <col min="4" max="4" width="40.5546875" customWidth="1"/>
-    <col min="7" max="7" width="21.109375" customWidth="1"/>
+    <col min="4" max="4" width="40.53125" customWidth="1"/>
+    <col min="7" max="7" width="21.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>33</v>
       </c>
@@ -995,7 +998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1005,7 +1008,7 @@
       <c r="E2" s="1"/>
       <c r="G2" s="16"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1015,7 +1018,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="30"/>
     </row>
-    <row r="4" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1024,7 +1027,7 @@
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1033,7 +1036,7 @@
       <c r="D5" s="3"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:7" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="91.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1043,7 +1046,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1053,7 +1056,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="14"/>
     </row>
-    <row r="8" spans="1:7" ht="84.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="84.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1064,7 +1067,7 @@
       <c r="F8" s="14"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1074,7 +1077,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="14"/>
     </row>
-    <row r="10" spans="1:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1085,7 +1088,7 @@
       <c r="F10" s="14"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1095,7 +1098,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="14"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1106,7 +1109,7 @@
       <c r="F12" s="14"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1116,7 +1119,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="14"/>
     </row>
-    <row r="14" spans="1:7" ht="71.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="71.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1125,7 +1128,7 @@
       <c r="D14" s="3"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1134,21 +1137,21 @@
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="39"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="36"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="36"/>
-      <c r="B17" s="36"/>
+    <row r="17" spans="1:10" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="33"/>
+      <c r="B17" s="33"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C18" s="4"/>
       <c r="G18" s="8"/>
       <c r="H18" s="9" t="s">
@@ -1161,7 +1164,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G19" s="10" t="s">
         <v>39</v>
       </c>
@@ -1178,7 +1181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G20" s="10" t="s">
         <v>40</v>
       </c>
@@ -1195,7 +1198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="G21" s="11" t="s">
         <v>30</v>
       </c>
@@ -1212,7 +1215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B22" s="29"/>
       <c r="G22" t="s">
         <v>41</v>
@@ -1222,7 +1225,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G23" t="s">
         <v>42</v>
       </c>
@@ -1238,7 +1241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G25" t="s">
         <v>43</v>
       </c>
@@ -1246,7 +1249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G26" t="s">
         <v>44</v>
       </c>
@@ -1267,40 +1270,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BC38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="39.44140625" customWidth="1"/>
-    <col min="18" max="18" width="9.5546875" customWidth="1"/>
-    <col min="19" max="20" width="8.5546875" customWidth="1"/>
-    <col min="21" max="21" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="5.1328125" customWidth="1"/>
+    <col min="2" max="2" width="39.46484375" customWidth="1"/>
+    <col min="18" max="18" width="9.53125" customWidth="1"/>
+    <col min="19" max="20" width="8.53125" customWidth="1"/>
+    <col min="21" max="21" width="8.86328125" customWidth="1"/>
     <col min="22" max="22" width="9.33203125" customWidth="1"/>
-    <col min="25" max="25" width="8.88671875" customWidth="1"/>
+    <col min="25" max="25" width="8.86328125" customWidth="1"/>
     <col min="48" max="48" width="10" customWidth="1"/>
-    <col min="55" max="55" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="10.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="C2" s="34" t="s">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="C2" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
       <c r="W2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1358,7 +1361,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1423,7 +1426,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1488,7 +1491,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1553,7 +1556,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1618,7 +1621,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1683,7 +1686,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1748,7 +1751,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1813,7 +1816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1878,7 +1881,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1943,7 +1946,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2008,7 +2011,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2073,7 +2076,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:35" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -2140,7 +2143,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2210,7 +2213,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:55" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:55" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2277,106 +2280,106 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:55" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:55" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="38">
         <v>1</v>
       </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33">
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38">
         <v>2</v>
       </c>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33">
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38">
         <v>3</v>
       </c>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33">
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38">
         <v>4</v>
       </c>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33">
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38">
         <v>5</v>
       </c>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33">
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38">
         <v>6</v>
       </c>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="33">
+      <c r="S21" s="38"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="38">
         <v>7</v>
       </c>
-      <c r="V21" s="33"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="33">
+      <c r="V21" s="38"/>
+      <c r="W21" s="38"/>
+      <c r="X21" s="38">
         <v>8</v>
       </c>
-      <c r="Y21" s="33"/>
-      <c r="Z21" s="33"/>
-      <c r="AA21" s="33">
+      <c r="Y21" s="38"/>
+      <c r="Z21" s="38"/>
+      <c r="AA21" s="38">
         <v>9</v>
       </c>
-      <c r="AB21" s="33"/>
-      <c r="AC21" s="33"/>
-      <c r="AD21" s="33">
+      <c r="AB21" s="38"/>
+      <c r="AC21" s="38"/>
+      <c r="AD21" s="38">
         <v>10</v>
       </c>
-      <c r="AE21" s="33"/>
-      <c r="AF21" s="33"/>
-      <c r="AG21" s="33">
+      <c r="AE21" s="38"/>
+      <c r="AF21" s="38"/>
+      <c r="AG21" s="38">
         <v>11</v>
       </c>
-      <c r="AH21" s="33"/>
-      <c r="AI21" s="33"/>
-      <c r="AJ21" s="33">
+      <c r="AH21" s="38"/>
+      <c r="AI21" s="38"/>
+      <c r="AJ21" s="38">
         <v>12</v>
       </c>
-      <c r="AK21" s="33"/>
-      <c r="AL21" s="33"/>
-      <c r="AM21" s="33">
+      <c r="AK21" s="38"/>
+      <c r="AL21" s="38"/>
+      <c r="AM21" s="38">
         <v>13</v>
       </c>
-      <c r="AN21" s="33"/>
-      <c r="AO21" s="33"/>
-      <c r="AP21" s="33">
+      <c r="AN21" s="38"/>
+      <c r="AO21" s="38"/>
+      <c r="AP21" s="38">
         <v>14</v>
       </c>
-      <c r="AQ21" s="33"/>
-      <c r="AR21" s="33"/>
-      <c r="AS21" s="33">
+      <c r="AQ21" s="38"/>
+      <c r="AR21" s="38"/>
+      <c r="AS21" s="38">
         <v>15</v>
       </c>
-      <c r="AT21" s="33"/>
-      <c r="AU21" s="33"/>
-      <c r="AV21" s="33" t="s">
+      <c r="AT21" s="38"/>
+      <c r="AU21" s="38"/>
+      <c r="AV21" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="AW21" s="33"/>
-      <c r="AX21" s="33"/>
-      <c r="AY21" s="33" t="s">
+      <c r="AW21" s="38"/>
+      <c r="AX21" s="38"/>
+      <c r="AY21" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="AZ21" s="33"/>
-      <c r="BA21" s="33"/>
-      <c r="BB21" s="33" t="s">
+      <c r="AZ21" s="38"/>
+      <c r="BA21" s="38"/>
+      <c r="BB21" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="BC21" s="33"/>
-    </row>
-    <row r="22" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BC21" s="38"/>
+    </row>
+    <row r="22" spans="1:55" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" t="s">
         <v>19</v>
       </c>
@@ -2413,9 +2416,9 @@
       <c r="AG22" s="6"/>
       <c r="AH22" s="6"/>
       <c r="AI22" s="6"/>
-      <c r="AJ22" s="35"/>
-      <c r="AK22" s="35"/>
-      <c r="AL22" s="35"/>
+      <c r="AJ22" s="37"/>
+      <c r="AK22" s="37"/>
+      <c r="AL22" s="37"/>
       <c r="AM22" s="6"/>
       <c r="AN22" s="6"/>
       <c r="AO22" s="6"/>
@@ -2426,7 +2429,7 @@
       <c r="AT22" s="6"/>
       <c r="AU22" s="6"/>
     </row>
-    <row r="23" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A23" s="8" t="s">
         <v>5</v>
       </c>
@@ -2593,7 +2596,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A24" s="10">
         <v>1</v>
       </c>
@@ -2769,7 +2772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A25" s="10">
         <v>2</v>
       </c>
@@ -2945,7 +2948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A26" s="10">
         <v>3</v>
       </c>
@@ -3115,7 +3118,7 @@
         <v>6.666666666666667</v>
       </c>
     </row>
-    <row r="27" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A27" s="10">
         <v>4</v>
       </c>
@@ -3291,7 +3294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A28" s="10">
         <v>5</v>
       </c>
@@ -3467,7 +3470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A29" s="10">
         <v>6</v>
       </c>
@@ -3643,7 +3646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A30" s="10">
         <v>7</v>
       </c>
@@ -3813,7 +3816,7 @@
         <v>6.666666666666667</v>
       </c>
     </row>
-    <row r="31" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A31" s="10">
         <v>8</v>
       </c>
@@ -3989,7 +3992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A32" s="10">
         <v>9</v>
       </c>
@@ -4159,7 +4162,7 @@
         <v>6.666666666666667</v>
       </c>
     </row>
-    <row r="33" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A33" s="10">
         <v>10</v>
       </c>
@@ -4335,7 +4338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A34" s="10">
         <v>11</v>
       </c>
@@ -4511,7 +4514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:55" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:55" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" s="10">
         <v>12</v>
       </c>
@@ -4687,7 +4690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:55" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:55" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36" s="10">
         <v>13</v>
       </c>
@@ -4863,7 +4866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:55" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:55" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" s="10">
         <v>14</v>
       </c>
@@ -5039,7 +5042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:55" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38" s="11"/>
       <c r="B38" s="12" t="s">
         <v>17</v>
@@ -5228,6 +5231,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="R21:T21"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
     <mergeCell ref="AJ22:AL22"/>
     <mergeCell ref="AV21:AX21"/>
     <mergeCell ref="AY21:BA21"/>
@@ -5241,13 +5251,6 @@
     <mergeCell ref="AM21:AO21"/>
     <mergeCell ref="AP21:AR21"/>
     <mergeCell ref="AS21:AU21"/>
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="R21:T21"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C24:AU37">
@@ -5267,40 +5270,40 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BC38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="39.44140625" customWidth="1"/>
-    <col min="18" max="18" width="7.88671875" customWidth="1"/>
-    <col min="19" max="20" width="8.5546875" customWidth="1"/>
-    <col min="21" max="21" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="5.1328125" customWidth="1"/>
+    <col min="2" max="2" width="39.46484375" customWidth="1"/>
+    <col min="18" max="18" width="7.86328125" customWidth="1"/>
+    <col min="19" max="20" width="8.53125" customWidth="1"/>
+    <col min="21" max="21" width="8.86328125" customWidth="1"/>
     <col min="22" max="22" width="9.33203125" customWidth="1"/>
-    <col min="25" max="25" width="8.88671875" customWidth="1"/>
+    <col min="25" max="25" width="8.86328125" customWidth="1"/>
     <col min="48" max="48" width="10" customWidth="1"/>
-    <col min="55" max="55" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="10.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="C2" s="34" t="s">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="C2" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
       <c r="W2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -5358,7 +5361,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -5423,7 +5426,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -5488,7 +5491,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -5553,7 +5556,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -5618,7 +5621,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -5683,7 +5686,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -5748,7 +5751,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -5813,7 +5816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -5878,7 +5881,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -5943,7 +5946,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -6008,7 +6011,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -6073,7 +6076,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -6138,7 +6141,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -6206,7 +6209,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -6275,106 +6278,106 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:55" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:55" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="38">
         <v>1</v>
       </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33">
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38">
         <v>2</v>
       </c>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33">
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38">
         <v>3</v>
       </c>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33">
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38">
         <v>4</v>
       </c>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33">
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38">
         <v>5</v>
       </c>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33">
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38">
         <v>6</v>
       </c>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="33">
+      <c r="S21" s="38"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="38">
         <v>7</v>
       </c>
-      <c r="V21" s="33"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="33">
+      <c r="V21" s="38"/>
+      <c r="W21" s="38"/>
+      <c r="X21" s="38">
         <v>8</v>
       </c>
-      <c r="Y21" s="33"/>
-      <c r="Z21" s="33"/>
-      <c r="AA21" s="33">
+      <c r="Y21" s="38"/>
+      <c r="Z21" s="38"/>
+      <c r="AA21" s="38">
         <v>9</v>
       </c>
-      <c r="AB21" s="33"/>
-      <c r="AC21" s="33"/>
-      <c r="AD21" s="33">
+      <c r="AB21" s="38"/>
+      <c r="AC21" s="38"/>
+      <c r="AD21" s="38">
         <v>10</v>
       </c>
-      <c r="AE21" s="33"/>
-      <c r="AF21" s="33"/>
-      <c r="AG21" s="33">
+      <c r="AE21" s="38"/>
+      <c r="AF21" s="38"/>
+      <c r="AG21" s="38">
         <v>11</v>
       </c>
-      <c r="AH21" s="33"/>
-      <c r="AI21" s="33"/>
-      <c r="AJ21" s="33">
+      <c r="AH21" s="38"/>
+      <c r="AI21" s="38"/>
+      <c r="AJ21" s="38">
         <v>12</v>
       </c>
-      <c r="AK21" s="33"/>
-      <c r="AL21" s="33"/>
-      <c r="AM21" s="33">
+      <c r="AK21" s="38"/>
+      <c r="AL21" s="38"/>
+      <c r="AM21" s="38">
         <v>13</v>
       </c>
-      <c r="AN21" s="33"/>
-      <c r="AO21" s="33"/>
-      <c r="AP21" s="33">
+      <c r="AN21" s="38"/>
+      <c r="AO21" s="38"/>
+      <c r="AP21" s="38">
         <v>14</v>
       </c>
-      <c r="AQ21" s="33"/>
-      <c r="AR21" s="33"/>
-      <c r="AS21" s="33">
+      <c r="AQ21" s="38"/>
+      <c r="AR21" s="38"/>
+      <c r="AS21" s="38">
         <v>15</v>
       </c>
-      <c r="AT21" s="33"/>
-      <c r="AU21" s="33"/>
-      <c r="AV21" s="33" t="s">
+      <c r="AT21" s="38"/>
+      <c r="AU21" s="38"/>
+      <c r="AV21" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="AW21" s="33"/>
-      <c r="AX21" s="33"/>
-      <c r="AY21" s="33" t="s">
+      <c r="AW21" s="38"/>
+      <c r="AX21" s="38"/>
+      <c r="AY21" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="AZ21" s="33"/>
-      <c r="BA21" s="33"/>
-      <c r="BB21" s="33" t="s">
+      <c r="AZ21" s="38"/>
+      <c r="BA21" s="38"/>
+      <c r="BB21" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="BC21" s="33"/>
-    </row>
-    <row r="22" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BC21" s="38"/>
+    </row>
+    <row r="22" spans="1:55" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" t="s">
         <v>19</v>
       </c>
@@ -6393,9 +6396,9 @@
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="35"/>
+      <c r="R22" s="37"/>
+      <c r="S22" s="37"/>
+      <c r="T22" s="37"/>
       <c r="U22" s="6"/>
       <c r="V22" s="6"/>
       <c r="W22" s="6"/>
@@ -6424,7 +6427,7 @@
       <c r="AT22" s="6"/>
       <c r="AU22" s="6"/>
     </row>
-    <row r="23" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A23" s="8" t="s">
         <v>5</v>
       </c>
@@ -6591,7 +6594,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A24" s="10">
         <v>1</v>
       </c>
@@ -6767,7 +6770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A25" s="10">
         <v>2</v>
       </c>
@@ -6943,7 +6946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A26" s="10">
         <v>3</v>
       </c>
@@ -7113,7 +7116,7 @@
         <v>6.666666666666667</v>
       </c>
     </row>
-    <row r="27" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A27" s="10">
         <v>4</v>
       </c>
@@ -7289,7 +7292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A28" s="10">
         <v>5</v>
       </c>
@@ -7459,7 +7462,7 @@
         <v>6.666666666666667</v>
       </c>
     </row>
-    <row r="29" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A29" s="10">
         <v>6</v>
       </c>
@@ -7629,7 +7632,7 @@
         <v>6.666666666666667</v>
       </c>
     </row>
-    <row r="30" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A30" s="10">
         <v>7</v>
       </c>
@@ -7799,7 +7802,7 @@
         <v>6.666666666666667</v>
       </c>
     </row>
-    <row r="31" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A31" s="10">
         <v>8</v>
       </c>
@@ -7969,7 +7972,7 @@
         <v>6.666666666666667</v>
       </c>
     </row>
-    <row r="32" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A32" s="10">
         <v>9</v>
       </c>
@@ -8139,7 +8142,7 @@
         <v>6.666666666666667</v>
       </c>
     </row>
-    <row r="33" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A33" s="10">
         <v>10</v>
       </c>
@@ -8309,7 +8312,7 @@
         <v>6.666666666666667</v>
       </c>
     </row>
-    <row r="34" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A34" s="10">
         <v>11</v>
       </c>
@@ -8485,7 +8488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A35" s="10">
         <v>12</v>
       </c>
@@ -8661,7 +8664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A36" s="10">
         <v>13</v>
       </c>
@@ -8837,7 +8840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A37" s="10">
         <v>14</v>
       </c>
@@ -9009,7 +9012,7 @@
         <v>4.4444444444444446</v>
       </c>
     </row>
-    <row r="38" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:55" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38" s="11"/>
       <c r="B38" s="12" t="s">
         <v>17</v>
@@ -9198,6 +9201,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="R21:T21"/>
+    <mergeCell ref="U21:W21"/>
+    <mergeCell ref="X21:Z21"/>
+    <mergeCell ref="AA21:AC21"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:N21"/>
     <mergeCell ref="R22:T22"/>
     <mergeCell ref="BB21:BC21"/>
     <mergeCell ref="AJ21:AL21"/>
@@ -9208,16 +9221,6 @@
     <mergeCell ref="AY21:BA21"/>
     <mergeCell ref="AG21:AI21"/>
     <mergeCell ref="AD21:AF21"/>
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="R21:T21"/>
-    <mergeCell ref="U21:W21"/>
-    <mergeCell ref="X21:Z21"/>
-    <mergeCell ref="AA21:AC21"/>
   </mergeCells>
   <conditionalFormatting sqref="C24:AU37">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
